--- a/jpcore-r4/feature/swg2-dental/CodeSystem-jp-documentcodes-cs.xlsx
+++ b/jpcore-r4/feature/swg2-dental/CodeSystem-jp-documentcodes-cs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="290">
   <si>
     <t>Property</t>
   </si>
@@ -129,7 +129,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>121</t>
+    <t>122</t>
   </si>
   <si>
     <t>Level</t>
@@ -586,6 +586,12 @@
   </si>
   <si>
     <t>微生物学的検査報告書</t>
+  </si>
+  <si>
+    <t>32453-3</t>
+  </si>
+  <si>
+    <t>口腔診査報告書</t>
   </si>
   <si>
     <t>34109-9</t>
@@ -1190,7 +1196,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D122"/>
+  <dimension ref="A1:D123"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -2085,7 +2091,7 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B75" t="s" s="2">
         <v>191</v>
@@ -2097,7 +2103,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B76" t="s" s="2">
         <v>193</v>
@@ -2421,7 +2427,7 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>247</v>
@@ -2429,21 +2435,21 @@
       <c r="C103" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="D103" t="s" s="2">
-        <v>249</v>
-      </c>
+      <c r="D103" s="2"/>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B104" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="C104" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="C104" t="s" s="2">
+      <c r="D104" t="s" s="2">
         <v>251</v>
       </c>
-      <c r="D104" s="2"/>
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
@@ -2483,7 +2489,7 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B108" t="s" s="2">
         <v>258</v>
@@ -2495,7 +2501,7 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B109" t="s" s="2">
         <v>260</v>
@@ -2531,7 +2537,7 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B112" t="s" s="2">
         <v>266</v>
@@ -2543,7 +2549,7 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B113" t="s" s="2">
         <v>268</v>
@@ -2555,7 +2561,7 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B114" t="s" s="2">
         <v>270</v>
@@ -2567,7 +2573,7 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B115" t="s" s="2">
         <v>272</v>
@@ -2591,7 +2597,7 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B117" t="s" s="2">
         <v>276</v>
@@ -2615,7 +2621,7 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B119" t="s" s="2">
         <v>280</v>
@@ -2627,7 +2633,7 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B120" t="s" s="2">
         <v>282</v>
@@ -2639,7 +2645,7 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B121" t="s" s="2">
         <v>284</v>
@@ -2651,7 +2657,7 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B122" t="s" s="2">
         <v>286</v>
@@ -2660,6 +2666,18 @@
         <v>287</v>
       </c>
       <c r="D122" s="2"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B123" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="C123" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="D123" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
